--- a/results_experiments/evoprompt_iter2/table/cluster_metrics_summary.xlsx
+++ b/results_experiments/evoprompt_iter2/table/cluster_metrics_summary.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programming\GitHub\LLM-PersonaBench\results_experiments\evoprompt_iter2\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4AC64A-238F-420C-96ED-B759079CE6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFE917B-C506-49AF-8695-27D5A8D7C7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Raw data" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист1" sheetId="3" r:id="rId2"/>
+    <sheet name="Raw data" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$3:$I$43</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="38">
   <si>
     <t>Сводная таблица по метрикам кластеров</t>
   </si>
@@ -42,12 +43,6 @@
   </si>
   <si>
     <t>MAE 35</t>
-  </si>
-  <si>
-    <t>Trace similarity</t>
-  </si>
-  <si>
-    <t>All similarity</t>
   </si>
   <si>
     <t>Valid share</t>
@@ -130,6 +125,21 @@
   <si>
     <t>after_optimization_test</t>
   </si>
+  <si>
+    <t>Mean similarity best evolution</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>Facet similarity</t>
+  </si>
+  <si>
+    <t>Trait similarity</t>
+  </si>
 </sst>
 </file>
 
@@ -166,7 +176,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,8 +221,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -247,12 +269,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -330,7 +397,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -342,10 +418,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -707,27 +819,27 @@
         <v>5</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="B4" s="36">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="15">
         <v>0.66491199999999995</v>
@@ -745,14 +857,14 @@
         <v>0.95</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="31"/>
-      <c r="B5" s="29"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="17">
         <v>0.71147400000000005</v>
@@ -770,16 +882,16 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="31"/>
-      <c r="B6" s="33">
+      <c r="A6" s="34"/>
+      <c r="B6" s="31">
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="16">
         <v>0.67553399999999997</v>
@@ -797,14 +909,14 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="31"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" s="17">
         <v>0.69050900000000004</v>
@@ -822,16 +934,16 @@
         <v>0.9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="31"/>
-      <c r="B8" s="29">
+      <c r="A8" s="34"/>
+      <c r="B8" s="36">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="15">
         <v>0.74041699999999999</v>
@@ -849,14 +961,14 @@
         <v>1</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="31"/>
-      <c r="B9" s="29"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" s="19">
         <v>0.73734</v>
@@ -874,16 +986,16 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="31"/>
-      <c r="B10" s="33">
+      <c r="A10" s="34"/>
+      <c r="B10" s="31">
         <v>3</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="16">
         <v>0.63713500000000001</v>
@@ -901,14 +1013,14 @@
         <v>1</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="32"/>
-      <c r="B11" s="34"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="32"/>
       <c r="C11" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="20">
         <v>0.67213500000000004</v>
@@ -926,18 +1038,18 @@
         <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="29">
+      <c r="A12" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="36">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="15">
         <v>0.653698</v>
@@ -955,14 +1067,14 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="31"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="17">
         <v>0.656667</v>
@@ -980,16 +1092,16 @@
         <v>1</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="31"/>
-      <c r="B14" s="33">
+      <c r="A14" s="34"/>
+      <c r="B14" s="31">
         <v>1</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="16">
         <v>0.63651000000000002</v>
@@ -1007,14 +1119,14 @@
         <v>1</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="31"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="17">
         <v>0.63817699999999999</v>
@@ -1032,16 +1144,16 @@
         <v>1</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29">
+      <c r="A16" s="34"/>
+      <c r="B16" s="36">
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="15">
         <v>0.68760399999999999</v>
@@ -1059,14 +1171,14 @@
         <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="31"/>
-      <c r="B17" s="29"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17" s="17">
         <v>0.71041699999999997</v>
@@ -1084,16 +1196,16 @@
         <v>1</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="31"/>
-      <c r="B18" s="33">
+      <c r="A18" s="34"/>
+      <c r="B18" s="31">
         <v>3</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="16">
         <v>0.64760399999999996</v>
@@ -1111,14 +1223,14 @@
         <v>1</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="32"/>
-      <c r="B19" s="34"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="20">
         <v>0.65229199999999998</v>
@@ -1136,18 +1248,18 @@
         <v>1</v>
       </c>
       <c r="I19" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="33" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="B20" s="36">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="15">
         <v>0.67265600000000003</v>
@@ -1165,14 +1277,14 @@
         <v>1</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="31"/>
-      <c r="B21" s="29"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" s="19">
         <v>0.67281199999999997</v>
@@ -1190,16 +1302,16 @@
         <v>1</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="31"/>
-      <c r="B22" s="33">
+      <c r="A22" s="34"/>
+      <c r="B22" s="31">
         <v>1</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" s="16">
         <v>0.67343799999999998</v>
@@ -1217,14 +1329,14 @@
         <v>1</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="31"/>
-      <c r="B23" s="33"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="31"/>
       <c r="C23" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" s="17">
         <v>0.67828100000000002</v>
@@ -1242,16 +1354,16 @@
         <v>1</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="31"/>
-      <c r="B24" s="29">
+      <c r="A24" s="34"/>
+      <c r="B24" s="36">
         <v>2</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="15">
         <v>0.69604200000000005</v>
@@ -1269,14 +1381,14 @@
         <v>1</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" s="17">
         <v>0.69703099999999996</v>
@@ -1294,16 +1406,16 @@
         <v>1</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="31"/>
-      <c r="B26" s="33">
+      <c r="A26" s="34"/>
+      <c r="B26" s="31">
         <v>3</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="16">
         <v>0.66953099999999999</v>
@@ -1321,14 +1433,14 @@
         <v>1</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="32"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="32"/>
       <c r="C27" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" s="20">
         <v>0.66963499999999998</v>
@@ -1346,18 +1458,18 @@
         <v>1</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="29">
+      <c r="A28" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="36">
         <v>0</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="15">
         <v>0.59729200000000005</v>
@@ -1375,14 +1487,14 @@
         <v>1</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="31"/>
-      <c r="B29" s="29"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D29" s="17">
         <v>0.59828099999999995</v>
@@ -1400,16 +1512,16 @@
         <v>1</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="31"/>
-      <c r="B30" s="33">
+      <c r="A30" s="34"/>
+      <c r="B30" s="31">
         <v>1</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" s="16">
         <v>0.58588499999999999</v>
@@ -1427,14 +1539,14 @@
         <v>1</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="31"/>
-      <c r="B31" s="33"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D31" s="19">
         <v>0.58291700000000002</v>
@@ -1452,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="31"/>
-      <c r="B32" s="29">
+      <c r="A32" s="34"/>
+      <c r="B32" s="36">
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" s="15">
         <v>0.65779900000000002</v>
@@ -1479,14 +1591,14 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="31"/>
-      <c r="B33" s="29"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D33" s="25">
         <v>0.65864599999999995</v>
@@ -1504,16 +1616,16 @@
         <v>1</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="31"/>
-      <c r="B34" s="33">
+      <c r="A34" s="34"/>
+      <c r="B34" s="31">
         <v>3</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D34" s="16">
         <v>0.61453100000000005</v>
@@ -1531,14 +1643,14 @@
         <v>1</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="32"/>
-      <c r="B35" s="34"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="32"/>
       <c r="C35" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D35" s="22">
         <v>0.61390599999999995</v>
@@ -1556,18 +1668,18 @@
         <v>1</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="29">
+      <c r="A36" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="36">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" s="15">
         <v>0.63677099999999998</v>
@@ -1585,14 +1697,14 @@
         <v>1</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="31"/>
-      <c r="B37" s="29"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D37" s="19">
         <v>0.63432299999999997</v>
@@ -1610,16 +1722,16 @@
         <v>1</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="31"/>
-      <c r="B38" s="33">
+      <c r="A38" s="34"/>
+      <c r="B38" s="31">
         <v>1</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38" s="16">
         <v>0.59567700000000001</v>
@@ -1637,14 +1749,14 @@
         <v>1</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="31"/>
-      <c r="B39" s="33"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D39" s="17">
         <v>0.61505200000000004</v>
@@ -1662,16 +1774,16 @@
         <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="31"/>
-      <c r="B40" s="29">
+      <c r="A40" s="34"/>
+      <c r="B40" s="36">
         <v>2</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40" s="15">
         <v>0.67812499999999998</v>
@@ -1689,14 +1801,14 @@
         <v>1</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="31"/>
-      <c r="B41" s="29"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D41" s="19">
         <v>0.67661499999999997</v>
@@ -1714,16 +1826,16 @@
         <v>1</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="31"/>
-      <c r="B42" s="33">
+      <c r="A42" s="34"/>
+      <c r="B42" s="31">
         <v>3</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D42" s="27">
         <v>0.64255200000000001</v>
@@ -1741,14 +1853,14 @@
         <v>1</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="32"/>
-      <c r="B43" s="34"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="32"/>
       <c r="C43" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D43" s="22">
         <v>0.64208299999999996</v>
@@ -1766,20 +1878,11 @@
         <v>1</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B14:B15"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="A20:A27"/>
     <mergeCell ref="B32:B33"/>
@@ -1796,12 +1899,1267 @@
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B14:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12529513-081D-403B-AAE5-238E45B08099}">
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D2" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="36">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.66491199999999995</v>
+      </c>
+      <c r="E4" s="4">
+        <v>24.595033000000001</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.78835500000000003</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.748332</v>
+      </c>
+      <c r="H4" s="48">
+        <v>0.71652300000000002</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="17">
+        <v>0.71147400000000005</v>
+      </c>
+      <c r="E5" s="18">
+        <v>26.105181000000002</v>
+      </c>
+      <c r="F5" s="19">
+        <v>0.78570300000000004</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0.73115600000000003</v>
+      </c>
+      <c r="H5" s="49"/>
+      <c r="I5" s="5">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="34"/>
+      <c r="B6" s="31">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0.67553399999999997</v>
+      </c>
+      <c r="E6" s="7">
+        <v>22.109148000000001</v>
+      </c>
+      <c r="F6" s="16">
+        <v>0.802485</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.77497899999999997</v>
+      </c>
+      <c r="H6" s="48">
+        <v>0.66759299999999999</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="34"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0.69050900000000004</v>
+      </c>
+      <c r="E7" s="18">
+        <v>22.738609</v>
+      </c>
+      <c r="F7" s="17">
+        <v>0.81526299999999996</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0.76550600000000002</v>
+      </c>
+      <c r="H7" s="49"/>
+      <c r="I7" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="34"/>
+      <c r="B8" s="36">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.74041699999999999</v>
+      </c>
+      <c r="E8" s="4">
+        <v>24.796030999999999</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.78387300000000004</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.74673400000000001</v>
+      </c>
+      <c r="H8" s="48">
+        <v>0.744201</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="34"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0.73734</v>
+      </c>
+      <c r="E9" s="18">
+        <v>25.318961000000002</v>
+      </c>
+      <c r="F9" s="19">
+        <v>0.77111300000000005</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0.74275999999999998</v>
+      </c>
+      <c r="H9" s="49"/>
+      <c r="I9" s="5">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="34"/>
+      <c r="B10" s="31">
+        <v>3</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0.63713500000000001</v>
+      </c>
+      <c r="E10" s="7">
+        <v>29.01989</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0.74428300000000003</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.70405399999999996</v>
+      </c>
+      <c r="H10" s="41">
+        <v>0.67861099999999996</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="35"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0.67213500000000004</v>
+      </c>
+      <c r="E11" s="21">
+        <v>27.697375000000001</v>
+      </c>
+      <c r="F11" s="22">
+        <v>0.73889700000000003</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.72038100000000005</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="10">
+        <v>1</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="36">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.653698</v>
+      </c>
+      <c r="E12" s="4">
+        <v>25.498964000000001</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.75895400000000002</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0.74268599999999996</v>
+      </c>
+      <c r="H12" s="43">
+        <v>0.65642400000000001</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="34"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0.656667</v>
+      </c>
+      <c r="E13" s="18">
+        <v>25.820734000000002</v>
+      </c>
+      <c r="F13" s="19">
+        <v>0.74759900000000001</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0.74082499999999996</v>
+      </c>
+      <c r="H13" s="40"/>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="34"/>
+      <c r="B14" s="31">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0.63651000000000002</v>
+      </c>
+      <c r="E14" s="7">
+        <v>23.746182000000001</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.75989700000000004</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.76297800000000005</v>
+      </c>
+      <c r="H14" s="41">
+        <v>0.62385400000000002</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="34"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="17">
+        <v>0.63817699999999999</v>
+      </c>
+      <c r="E15" s="18">
+        <v>23.801268</v>
+      </c>
+      <c r="F15" s="19">
+        <v>0.76078000000000001</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0.76218900000000001</v>
+      </c>
+      <c r="H15" s="42"/>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="34"/>
+      <c r="B16" s="36">
+        <v>2</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0.68760399999999999</v>
+      </c>
+      <c r="E16" s="4">
+        <v>26.924983999999998</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0.78014799999999995</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0.72251699999999996</v>
+      </c>
+      <c r="H16" s="39">
+        <v>0.71444399999999997</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="34"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0.71041699999999997</v>
+      </c>
+      <c r="E17" s="23">
+        <v>24.774163999999999</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0.76668700000000001</v>
+      </c>
+      <c r="G17" s="17">
+        <v>0.74985400000000002</v>
+      </c>
+      <c r="H17" s="40"/>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="34"/>
+      <c r="B18" s="31">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.64760399999999996</v>
+      </c>
+      <c r="E18" s="7">
+        <v>28.433243999999998</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0.77600599999999997</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.70561099999999999</v>
+      </c>
+      <c r="H18" s="41">
+        <v>0.66958300000000004</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="35"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="20">
+        <v>0.65229199999999998</v>
+      </c>
+      <c r="E19" s="24">
+        <v>29.611810999999999</v>
+      </c>
+      <c r="F19" s="22">
+        <v>0.75672099999999998</v>
+      </c>
+      <c r="G19" s="22">
+        <v>0.695075</v>
+      </c>
+      <c r="H19" s="44"/>
+      <c r="I19" s="10">
+        <v>1</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="36">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0.67265600000000003</v>
+      </c>
+      <c r="E20" s="4">
+        <v>22.892443</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.80459400000000003</v>
+      </c>
+      <c r="G20" s="15">
+        <v>0.76548899999999998</v>
+      </c>
+      <c r="H20" s="43">
+        <v>0.671319</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="34"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="19">
+        <v>0.67281199999999997</v>
+      </c>
+      <c r="E21" s="18">
+        <v>22.901610000000002</v>
+      </c>
+      <c r="F21" s="17">
+        <v>0.80624700000000005</v>
+      </c>
+      <c r="G21" s="19">
+        <v>0.76510699999999998</v>
+      </c>
+      <c r="H21" s="40"/>
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="34"/>
+      <c r="B22" s="31">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0.67343799999999998</v>
+      </c>
+      <c r="E22" s="7">
+        <v>19.354140999999998</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.84612399999999999</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0.799848</v>
+      </c>
+      <c r="H22" s="41">
+        <v>0.65718699999999997</v>
+      </c>
+      <c r="I22" s="8">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="34"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="17">
+        <v>0.67828100000000002</v>
+      </c>
+      <c r="E23" s="23">
+        <v>19.135822000000001</v>
+      </c>
+      <c r="F23" s="17">
+        <v>0.85512100000000002</v>
+      </c>
+      <c r="G23" s="17">
+        <v>0.80089500000000002</v>
+      </c>
+      <c r="H23" s="46"/>
+      <c r="I23" s="8">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="34"/>
+      <c r="B24" s="36">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="15">
+        <v>0.69604200000000005</v>
+      </c>
+      <c r="E24" s="4">
+        <v>25.546938999999998</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.76159200000000005</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0.74168699999999999</v>
+      </c>
+      <c r="H24" s="47">
+        <v>0.70604199999999995</v>
+      </c>
+      <c r="I24" s="5">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="34"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="17">
+        <v>0.69703099999999996</v>
+      </c>
+      <c r="E25" s="23">
+        <v>25.355291000000001</v>
+      </c>
+      <c r="F25" s="17">
+        <v>0.77354999999999996</v>
+      </c>
+      <c r="G25" s="17">
+        <v>0.74192999999999998</v>
+      </c>
+      <c r="H25" s="40"/>
+      <c r="I25" s="5">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="34"/>
+      <c r="B26" s="31">
+        <v>3</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="16">
+        <v>0.66953099999999999</v>
+      </c>
+      <c r="E26" s="7">
+        <v>27.289916000000002</v>
+      </c>
+      <c r="F26" s="16">
+        <v>0.74915500000000002</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0.72342499999999998</v>
+      </c>
+      <c r="H26" s="41">
+        <v>0.68465299999999996</v>
+      </c>
+      <c r="I26" s="8">
+        <v>1</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="35"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="20">
+        <v>0.66963499999999998</v>
+      </c>
+      <c r="E27" s="21">
+        <v>27.042202</v>
+      </c>
+      <c r="F27" s="20">
+        <v>0.759552</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0.72458199999999995</v>
+      </c>
+      <c r="H27" s="44"/>
+      <c r="I27" s="10">
+        <v>1</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="36">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="15">
+        <v>0.59729200000000005</v>
+      </c>
+      <c r="E28" s="4">
+        <v>28.131612000000001</v>
+      </c>
+      <c r="F28" s="15">
+        <v>0.71398200000000001</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0.719468</v>
+      </c>
+      <c r="H28" s="43">
+        <v>0.60322900000000002</v>
+      </c>
+      <c r="I28" s="5">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="34"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="17">
+        <v>0.59828099999999995</v>
+      </c>
+      <c r="E29" s="18">
+        <v>28.510134999999998</v>
+      </c>
+      <c r="F29" s="19">
+        <v>0.70985299999999996</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.71574000000000004</v>
+      </c>
+      <c r="H29" s="40"/>
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="34"/>
+      <c r="B30" s="31">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="16">
+        <v>0.58588499999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>27.030335999999998</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.72457000000000005</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0.73055099999999995</v>
+      </c>
+      <c r="H30" s="41">
+        <v>0.57885399999999998</v>
+      </c>
+      <c r="I30" s="8">
+        <v>1</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="34"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="19">
+        <v>0.58291700000000002</v>
+      </c>
+      <c r="E31" s="18">
+        <v>27.472636000000001</v>
+      </c>
+      <c r="F31" s="25">
+        <v>0.72929699999999997</v>
+      </c>
+      <c r="G31" s="19">
+        <v>0.724603</v>
+      </c>
+      <c r="H31" s="42"/>
+      <c r="I31" s="8">
+        <v>1</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="34"/>
+      <c r="B32" s="36">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="15">
+        <v>0.65779900000000002</v>
+      </c>
+      <c r="E32" s="4">
+        <v>30.014446</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.72606400000000004</v>
+      </c>
+      <c r="G32" s="15">
+        <v>0.695488</v>
+      </c>
+      <c r="H32" s="39">
+        <v>0.65208299999999997</v>
+      </c>
+      <c r="I32" s="5">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="34"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="25">
+        <v>0.65864599999999995</v>
+      </c>
+      <c r="E33" s="26">
+        <v>29.433657</v>
+      </c>
+      <c r="F33" s="25">
+        <v>0.72934299999999996</v>
+      </c>
+      <c r="G33" s="25">
+        <v>0.70171700000000004</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="5">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="34"/>
+      <c r="B34" s="31">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="16">
+        <v>0.61453100000000005</v>
+      </c>
+      <c r="E34" s="7">
+        <v>29.376182</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0.72527299999999995</v>
+      </c>
+      <c r="G34" s="16">
+        <v>0.70306599999999997</v>
+      </c>
+      <c r="H34" s="41">
+        <v>0.62402800000000003</v>
+      </c>
+      <c r="I34" s="8">
+        <v>1</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="35"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="22">
+        <v>0.61390599999999995</v>
+      </c>
+      <c r="E35" s="24">
+        <v>29.782893000000001</v>
+      </c>
+      <c r="F35" s="22">
+        <v>0.72198600000000002</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0.69886899999999996</v>
+      </c>
+      <c r="H35" s="44"/>
+      <c r="I35" s="10">
+        <v>1</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="36">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="15">
+        <v>0.63677099999999998</v>
+      </c>
+      <c r="E36" s="4">
+        <v>25.160848999999999</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0.77047699999999997</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.74471100000000001</v>
+      </c>
+      <c r="H36" s="43">
+        <v>0.63951400000000003</v>
+      </c>
+      <c r="I36" s="5">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="34"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="19">
+        <v>0.63432299999999997</v>
+      </c>
+      <c r="E37" s="18">
+        <v>25.480654999999999</v>
+      </c>
+      <c r="F37" s="19">
+        <v>0.76499799999999996</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0.74189300000000002</v>
+      </c>
+      <c r="H37" s="40"/>
+      <c r="I37" s="5">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="34"/>
+      <c r="B38" s="31">
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="16">
+        <v>0.59567700000000001</v>
+      </c>
+      <c r="E38" s="7">
+        <v>24.224504</v>
+      </c>
+      <c r="F38" s="16">
+        <v>0.78403299999999998</v>
+      </c>
+      <c r="G38" s="16">
+        <v>0.75337500000000002</v>
+      </c>
+      <c r="H38" s="41">
+        <v>0.59961799999999998</v>
+      </c>
+      <c r="I38" s="8">
+        <v>1</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="34"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="17">
+        <v>0.61505200000000004</v>
+      </c>
+      <c r="E39" s="23">
+        <v>23.742013</v>
+      </c>
+      <c r="F39" s="17">
+        <v>0.78564000000000001</v>
+      </c>
+      <c r="G39" s="17">
+        <v>0.75873699999999999</v>
+      </c>
+      <c r="H39" s="42"/>
+      <c r="I39" s="8">
+        <v>1</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="34"/>
+      <c r="B40" s="36">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="15">
+        <v>0.67812499999999998</v>
+      </c>
+      <c r="E40" s="4">
+        <v>27.190425999999999</v>
+      </c>
+      <c r="F40" s="15">
+        <v>0.76199399999999995</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0.72244600000000003</v>
+      </c>
+      <c r="H40" s="39">
+        <v>0.67843699999999996</v>
+      </c>
+      <c r="I40" s="5">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="34"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="19">
+        <v>0.67661499999999997</v>
+      </c>
+      <c r="E41" s="18">
+        <v>28.915459999999999</v>
+      </c>
+      <c r="F41" s="19">
+        <v>0.73468199999999995</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0.70687299999999997</v>
+      </c>
+      <c r="H41" s="40"/>
+      <c r="I41" s="5">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" s="34"/>
+      <c r="B42" s="31">
+        <v>3</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="27">
+        <v>0.64255200000000001</v>
+      </c>
+      <c r="E42" s="28">
+        <v>30.830760000000001</v>
+      </c>
+      <c r="F42" s="27">
+        <v>0.699743</v>
+      </c>
+      <c r="G42" s="27">
+        <v>0.69035100000000005</v>
+      </c>
+      <c r="H42" s="37">
+        <v>0.651285</v>
+      </c>
+      <c r="I42" s="8">
+        <v>1</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="35"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="22">
+        <v>0.64208299999999996</v>
+      </c>
+      <c r="E43" s="24">
+        <v>31.239484000000001</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0.69919600000000004</v>
+      </c>
+      <c r="G43" s="22">
+        <v>0.68567299999999998</v>
+      </c>
+      <c r="H43" s="38"/>
+      <c r="I43" s="10">
+        <v>1</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A20:A27"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A35"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A4:A11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1817,54 +3175,54 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" s="12">
         <v>0.66491199999999995</v>
@@ -1879,13 +3237,13 @@
         <v>0.78835500000000003</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2" s="14">
         <v>0.95</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L2" s="14">
         <v>0.95</v>
@@ -1893,16 +3251,16 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="12">
         <v>0.71147400000000005</v>
@@ -1917,13 +3275,13 @@
         <v>0.78570300000000004</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3" s="14">
         <v>0.97499999999999998</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L3" s="14">
         <v>0.97499999999999998</v>
@@ -1931,16 +3289,16 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" s="12">
         <v>0.67553399999999997</v>
@@ -1955,13 +3313,13 @@
         <v>0.802485</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" s="14">
         <v>0.97499999999999998</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L4" s="14">
         <v>0.97499999999999998</v>
@@ -1969,16 +3327,16 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="12">
         <v>0.69050900000000004</v>
@@ -1993,13 +3351,13 @@
         <v>0.81526299999999996</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J5" s="14">
         <v>0.9</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L5" s="14">
         <v>0.9</v>
@@ -2007,16 +3365,16 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" s="12">
         <v>0.74041699999999999</v>
@@ -2031,13 +3389,13 @@
         <v>0.78387300000000004</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J6" s="14">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L6" s="14">
         <v>1</v>
@@ -2045,16 +3403,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E7" s="12">
         <v>0.73734</v>
@@ -2069,13 +3427,13 @@
         <v>0.77111300000000005</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J7" s="14">
         <v>0.97499999999999998</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L7" s="14">
         <v>0.97499999999999998</v>
@@ -2083,16 +3441,16 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" s="12">
         <v>0.63713500000000001</v>
@@ -2107,13 +3465,13 @@
         <v>0.74428300000000003</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J8" s="14">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L8" s="14">
         <v>1</v>
@@ -2121,16 +3479,16 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" s="12">
         <v>0.67213500000000004</v>
@@ -2145,13 +3503,13 @@
         <v>0.73889700000000003</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J9" s="14">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L9" s="14">
         <v>1</v>
@@ -2159,16 +3517,16 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="12">
         <v>0.653698</v>
@@ -2183,13 +3541,13 @@
         <v>0.75895400000000002</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J10" s="14">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L10" s="14">
         <v>1</v>
@@ -2197,16 +3555,16 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" s="12">
         <v>0.656667</v>
@@ -2221,13 +3579,13 @@
         <v>0.74759900000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J11" s="14">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L11" s="14">
         <v>1</v>
@@ -2235,16 +3593,16 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" s="12">
         <v>0.63651000000000002</v>
@@ -2259,13 +3617,13 @@
         <v>0.75989700000000004</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J12" s="14">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
@@ -2273,16 +3631,16 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="12">
         <v>0.63817699999999999</v>
@@ -2297,13 +3655,13 @@
         <v>0.76078000000000001</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J13" s="14">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L13" s="14">
         <v>1</v>
@@ -2311,16 +3669,16 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" s="12">
         <v>0.68760399999999999</v>
@@ -2335,13 +3693,13 @@
         <v>0.78014799999999995</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L14" s="14">
         <v>1</v>
@@ -2349,16 +3707,16 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" s="12">
         <v>0.71041699999999997</v>
@@ -2373,13 +3731,13 @@
         <v>0.76668700000000001</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L15" s="14">
         <v>1</v>
@@ -2387,16 +3745,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" s="12">
         <v>0.64760399999999996</v>
@@ -2411,13 +3769,13 @@
         <v>0.77600599999999997</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L16" s="14">
         <v>1</v>
@@ -2425,16 +3783,16 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E17" s="12">
         <v>0.65229199999999998</v>
@@ -2449,13 +3807,13 @@
         <v>0.75672099999999998</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J17" s="14">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L17" s="14">
         <v>1</v>
@@ -2463,16 +3821,16 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" s="12">
         <v>0.67265600000000003</v>
@@ -2487,13 +3845,13 @@
         <v>0.80459400000000003</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L18" s="14">
         <v>1</v>
@@ -2501,16 +3859,16 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E19" s="12">
         <v>0.67281199999999997</v>
@@ -2525,13 +3883,13 @@
         <v>0.80624700000000005</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J19" s="14">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L19" s="14">
         <v>1</v>
@@ -2539,16 +3897,16 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E20" s="12">
         <v>0.67343799999999998</v>
@@ -2563,13 +3921,13 @@
         <v>0.84612399999999999</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J20" s="14">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L20" s="14">
         <v>1</v>
@@ -2577,16 +3935,16 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E21" s="12">
         <v>0.67828100000000002</v>
@@ -2601,13 +3959,13 @@
         <v>0.85512100000000002</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J21" s="14">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L21" s="14">
         <v>1</v>
@@ -2615,16 +3973,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22" s="12">
         <v>0.69604200000000005</v>
@@ -2639,13 +3997,13 @@
         <v>0.76159200000000005</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L22" s="14">
         <v>1</v>
@@ -2653,16 +4011,16 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="12">
         <v>0.69703099999999996</v>
@@ -2677,13 +4035,13 @@
         <v>0.77354999999999996</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L23" s="14">
         <v>1</v>
@@ -2691,16 +4049,16 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E24" s="12">
         <v>0.66953099999999999</v>
@@ -2715,13 +4073,13 @@
         <v>0.74915500000000002</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J24" s="14">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -2729,16 +4087,16 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" s="12">
         <v>0.66963499999999998</v>
@@ -2753,13 +4111,13 @@
         <v>0.759552</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J25" s="14">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L25" s="14">
         <v>1</v>
@@ -2767,16 +4125,16 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E26" s="12">
         <v>0.59729200000000005</v>
@@ -2791,13 +4149,13 @@
         <v>0.71398200000000001</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J26" s="14">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -2805,16 +4163,16 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="12">
         <v>0.59828099999999995</v>
@@ -2829,13 +4187,13 @@
         <v>0.70985299999999996</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L27" s="14">
         <v>1</v>
@@ -2843,16 +4201,16 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E28" s="12">
         <v>0.58588499999999999</v>
@@ -2867,13 +4225,13 @@
         <v>0.72457000000000005</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L28" s="14">
         <v>1</v>
@@ -2881,16 +4239,16 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" s="12">
         <v>0.58291700000000002</v>
@@ -2905,13 +4263,13 @@
         <v>0.72929699999999997</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L29" s="14">
         <v>1</v>
@@ -2919,16 +4277,16 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E30" s="12">
         <v>0.65779900000000002</v>
@@ -2943,13 +4301,13 @@
         <v>0.72606400000000004</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J30" s="14">
         <v>0.97499999999999998</v>
       </c>
       <c r="K30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L30" s="14">
         <v>0.97499999999999998</v>
@@ -2957,16 +4315,16 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" s="12">
         <v>0.65864599999999995</v>
@@ -2981,13 +4339,13 @@
         <v>0.72934299999999996</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L31" s="14">
         <v>1</v>
@@ -2995,16 +4353,16 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E32" s="12">
         <v>0.61453100000000005</v>
@@ -3019,13 +4377,13 @@
         <v>0.72527299999999995</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J32" s="14">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L32" s="14">
         <v>1</v>
@@ -3033,16 +4391,16 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E33" s="12">
         <v>0.61390599999999995</v>
@@ -3057,13 +4415,13 @@
         <v>0.72198600000000002</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L33" s="14">
         <v>1</v>
@@ -3071,16 +4429,16 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E34" s="12">
         <v>0.63677099999999998</v>
@@ -3095,13 +4453,13 @@
         <v>0.77047699999999997</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J34" s="14">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L34" s="14">
         <v>1</v>
@@ -3109,16 +4467,16 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E35" s="12">
         <v>0.63432299999999997</v>
@@ -3133,13 +4491,13 @@
         <v>0.76499799999999996</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J35" s="14">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L35" s="14">
         <v>1</v>
@@ -3147,16 +4505,16 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E36" s="12">
         <v>0.59567700000000001</v>
@@ -3171,13 +4529,13 @@
         <v>0.78403299999999998</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J36" s="14">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L36" s="14">
         <v>1</v>
@@ -3185,16 +4543,16 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E37" s="12">
         <v>0.61505200000000004</v>
@@ -3209,13 +4567,13 @@
         <v>0.78564000000000001</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J37" s="14">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L37" s="14">
         <v>1</v>
@@ -3223,16 +4581,16 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E38" s="12">
         <v>0.67812499999999998</v>
@@ -3247,13 +4605,13 @@
         <v>0.76199399999999995</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J38" s="14">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L38" s="14">
         <v>1</v>
@@ -3261,16 +4619,16 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E39" s="12">
         <v>0.67661499999999997</v>
@@ -3285,13 +4643,13 @@
         <v>0.73468199999999995</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J39" s="14">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L39" s="14">
         <v>1</v>
@@ -3299,16 +4657,16 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E40" s="12">
         <v>0.64255200000000001</v>
@@ -3323,13 +4681,13 @@
         <v>0.699743</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J40" s="14">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L40" s="14">
         <v>1</v>
@@ -3337,16 +4695,16 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E41" s="12">
         <v>0.64208299999999996</v>
@@ -3361,13 +4719,13 @@
         <v>0.69919600000000004</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J41" s="14">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L41" s="14">
         <v>1</v>
